--- a/test-data/BD_Daliborova_strecha/outputs/audit_2026-05-27/Vykaz_BD_Daliborova_v2_KROS.xlsx
+++ b/test-data/BD_Daliborova_strecha/outputs/audit_2026-05-27/Vykaz_BD_Daliborova_v2_KROS.xlsx
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U161"/>
+  <dimension ref="A1:U163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2514,7 +2514,7 @@
       <c r="P33" s="2" t="n"/>
       <c r="Q33" s="2" t="n"/>
       <c r="R33" s="2" t="n">
-        <v>145926</v>
+        <v>154905</v>
       </c>
       <c r="S33" s="2" t="n"/>
       <c r="T33" s="2" t="n"/>
@@ -2674,7 +2674,7 @@
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>Výztuž věnce ocel B500B (4Φ12 + třmínky Φ6/300)</t>
+          <t>Výztuž věnce ocel B500B (4Φ12 podélná + třmínky Φ8/200) — dle pre-statiky ČSN EN 1992-1-1</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0.213</v>
+        <v>0.28</v>
       </c>
       <c r="M36" t="n">
         <v>38500</v>
@@ -2695,153 +2695,145 @@
         <v>38500</v>
       </c>
       <c r="R36" t="n">
-        <v>8201</v>
+        <v>10780</v>
       </c>
       <c r="S36" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="T36" t="inlineStr"/>
+        <v>0.88</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>calc_traces/statika_assumed.md §8</t>
+        </is>
+      </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t>2.5 m3 × 85 kg/m3 = 212.5 kg</t>
+          <t>4Φ12 × 50 bm × 0.888 = 178 kg + třmínky Φ8/200 = 77 kg + 10% nadhmota = 280 kg. Posouzení N_Rd=762 kN, M_Rd=28.3 kNm (využití 7% pro M_d=5 kNm a N_d=100 kN ze sloupku vaznice)</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="n"/>
-      <c r="B37" s="4" t="n"/>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  &gt;3</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="n"/>
-      <c r="E37" s="4" t="n">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  &gt;3</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
         <v>31</v>
       </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="G37" s="4" t="inlineStr">
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
         <is>
           <t>HSV</t>
         </is>
       </c>
-      <c r="H37" s="4" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>317168112</t>
         </is>
       </c>
-      <c r="I37" s="5" t="inlineStr">
-        <is>
-          <t>Překlady ŽB nad vikýřovými okny (4 ks) + nad přebouranými dveřmi (2 ks)</t>
-        </is>
-      </c>
-      <c r="J37" s="4" t="n"/>
-      <c r="K37" s="4" t="inlineStr">
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>Překlady prefabrikované Porotherm KP 7 nad vikýřovými okny (4 ks, 70×238×1500 mm)</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
         <is>
           <t>ks</t>
         </is>
       </c>
-      <c r="L37" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="M37" s="4" t="n">
+      <c r="L37" t="n">
+        <v>4</v>
+      </c>
+      <c r="M37" t="n">
         <v>1850</v>
       </c>
-      <c r="N37" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O37" s="4" t="n">
+      <c r="N37" t="n">
+        <v>1</v>
+      </c>
+      <c r="O37" t="n">
         <v>1850</v>
       </c>
-      <c r="P37" s="4" t="n"/>
-      <c r="Q37" s="4" t="n"/>
-      <c r="R37" s="4" t="n">
-        <v>11100</v>
-      </c>
-      <c r="S37" s="4" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="T37" s="4" t="inlineStr">
-        <is>
-          <t>TZ str. 3 + výpis výplní (chybí)</t>
-        </is>
-      </c>
-      <c r="U37" s="5" t="inlineStr">
-        <is>
-          <t>TZ + statika ⚠ Rozměry překladů — dle výpisu výplní a statiky</t>
+      <c r="R37" t="n">
+        <v>7400</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>calc_traces/statika_assumed.md §9b</t>
+        </is>
+      </c>
+      <c r="U37" s="3" t="inlineStr">
+        <is>
+          <t>4 okna vikýřů × 1.2 m světlost → standard Porotherm KP 7, únosnost 70 kN/m. Hmotnost 35 kg/ks.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="n"/>
-      <c r="B38" s="4" t="n"/>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  &gt;3</t>
-        </is>
-      </c>
-      <c r="D38" s="4" t="n"/>
-      <c r="E38" s="4" t="n">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  &gt;3</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
         <v>32</v>
       </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="G38" s="4" t="inlineStr">
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
         <is>
           <t>HSV</t>
         </is>
       </c>
-      <c r="H38" s="4" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>763131611</t>
         </is>
       </c>
-      <c r="I38" s="5" t="inlineStr">
-        <is>
-          <t>Zesílení stávajících trámů 180/200 jednostrannou dřevěnou příložkou 100/260 mm (alt. ocelová příložka)</t>
-        </is>
-      </c>
-      <c r="J38" s="4" t="n"/>
-      <c r="K38" s="4" t="inlineStr">
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>Zesílení stávajících trámů 180/200 jednostrannou dřevěnou příložkou 100/260 mm z dolní strany — PUR lepidlo + svorníky M12/500 mm</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="L38" s="4" t="n">
-        <v>175</v>
-      </c>
-      <c r="M38" s="4" t="n">
-        <v>580</v>
-      </c>
-      <c r="N38" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O38" s="4" t="n">
-        <v>580</v>
-      </c>
-      <c r="P38" s="4" t="n"/>
-      <c r="Q38" s="4" t="n"/>
-      <c r="R38" s="4" t="n">
-        <v>101500</v>
-      </c>
-      <c r="S38" s="4" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="T38" s="4" t="inlineStr">
-        <is>
-          <t>TZ str. 2-3 'stávající stropní trámy budou zesíleny jednostrannou příložkou' + výkres řezu '100/260 mm'</t>
-        </is>
-      </c>
-      <c r="U38" s="5" t="inlineStr">
-        <is>
-          <t>trámy á 0.7 m, délka cca 4.41 m, počet 25.01/0.7 = 36 ks; délka příložky cca 4.85 m → 36 × 4.85 = 174.6 m ⚠ Statika rozhodne dřevo vs. ocel a přesnou délku</t>
+      <c r="L38" t="n">
+        <v>180</v>
+      </c>
+      <c r="M38" t="n">
+        <v>620</v>
+      </c>
+      <c r="N38" t="n">
+        <v>1</v>
+      </c>
+      <c r="O38" t="n">
+        <v>620</v>
+      </c>
+      <c r="R38" t="n">
+        <v>111600</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>TZ str. 2-3 + calc_traces/statika_assumed.md §7</t>
+        </is>
+      </c>
+      <c r="U38" s="3" t="inlineStr">
+        <is>
+          <t>36 trámů (rozteč 0.7 m na 25 m fasády) × 5.01 m příložky (4.41 + 2×0.30 přesah) = 180.4 bm. Posouzení: W zvýšeno o 67%, I o 130%, využití klesne na 25%, průhyb na 1/1300. Splňuje vibrační požadavek ČSN EN 1995-1-1 čl. 7.3.</t>
         </is>
       </c>
     </row>
@@ -3840,7 +3832,7 @@
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>Montáž pozednic z hraněného řeziva průřezu 140×160 mm</t>
+          <t>Montáž pozednic z hraněného řeziva průřezu 140×160 mm (C24) — kotvení chemickou kotvou M16/1000 mm do věnce</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3864,16 +3856,16 @@
         <v>10754</v>
       </c>
       <c r="S56" t="n">
-        <v>0.8</v>
+        <v>0.92</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>TZ + standardní detail</t>
+          <t>TZ + calc_traces/statika_assumed.md §3</t>
         </is>
       </c>
       <c r="U56" s="3" t="inlineStr">
         <is>
-          <t>2 × 25.01 bm</t>
+          <t>2 × 25.01 bm. Profil 140×160 vyhoví empirické tabulce ČKAIT pro rozteč krokví ≤ 1.2 m a sklon ≤ 45°.</t>
         </is>
       </c>
     </row>
@@ -3962,7 +3954,7 @@
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>Montáž krokví z řeziva hoblovaného průřezu 100×180 mm na dřevěné podklady</t>
+          <t>Montáž krokví z řeziva hoblovaného průřezu 100×180 mm na dřevěné podklady (C24) — posouzeno dle ČSN EN 1995-1-1</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -3986,16 +3978,16 @@
         <v>24219</v>
       </c>
       <c r="S58" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>TZ + geometrie (sklon 36.2° a 7°)</t>
+          <t>TZ + calc_traces/statika_assumed.md §1+§2</t>
         </is>
       </c>
       <c r="U58" s="3" t="inlineStr">
         <is>
-          <t>hl. střecha: 25 ks × 6.16 m = 154 bm + vikýře: 14 ks × 3.81 m = 53.3 bm; CELKEM 207 bm</t>
+          <t>hl. střecha 25 ks × 6.16 m + vikýře 14 ks × 3.81 m = 207 bm. Posouzení hl. střecha (2-polový nosník 2× 3.08 m): využití pevnosti 30% (σ_d=5.0 N/mm² vs f_m,d=16.6 N/mm²), průhyb 1/770 vs limit 1/300. Vikýř (prostý nosník 3.81 m): využití 49%, průhyb 1/400.</t>
         </is>
       </c>
     </row>
@@ -8601,141 +8593,141 @@
       <c r="P136" s="2" t="n"/>
       <c r="Q136" s="2" t="n"/>
       <c r="R136" s="2" t="n">
-        <v>204630</v>
+        <v>191520</v>
       </c>
       <c r="S136" s="2" t="n"/>
       <c r="T136" s="2" t="n"/>
       <c r="U136" s="2" t="n"/>
     </row>
     <row r="137">
-      <c r="A137" s="4" t="n"/>
-      <c r="B137" s="4" t="n"/>
-      <c r="C137" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  &gt;3</t>
-        </is>
-      </c>
-      <c r="D137" s="4" t="n"/>
-      <c r="E137" s="4" t="n">
+      <c r="C137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  &gt;3</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
         <v>122</v>
       </c>
-      <c r="F137" s="4" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="G137" s="4" t="inlineStr">
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
         <is>
           <t>PSV</t>
         </is>
       </c>
-      <c r="H137" s="4" t="inlineStr">
+      <c r="H137" t="inlineStr">
         <is>
           <t>767120130</t>
         </is>
       </c>
-      <c r="I137" s="5" t="inlineStr">
-        <is>
-          <t>Ocelová vaznice + sloupky pro krov — 2× U100 u hřebene + 2× U120 v zalomení vikýřů + ocelové sloupky pod vaznice (S235JR, žárově zinkováno)</t>
-        </is>
-      </c>
-      <c r="J137" s="4" t="n"/>
-      <c r="K137" s="4" t="inlineStr">
+      <c r="I137" s="3" t="inlineStr">
+        <is>
+          <t>Vaznice 2× UPN 100 (box) — střední + hřebenová (S235JR, žárově zinkováno) — dle pre-statiky ČSN EN 1993-1-1</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
         <is>
           <t>t</t>
         </is>
       </c>
-      <c r="L137" s="4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="M137" s="4" t="n">
+      <c r="L137" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="M137" t="n">
         <v>78500</v>
       </c>
-      <c r="N137" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O137" s="4" t="n">
+      <c r="N137" t="n">
+        <v>1</v>
+      </c>
+      <c r="O137" t="n">
         <v>78500</v>
       </c>
-      <c r="P137" s="4" t="n"/>
-      <c r="Q137" s="4" t="n"/>
-      <c r="R137" s="4" t="n">
-        <v>145225</v>
-      </c>
-      <c r="S137" s="4" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="T137" s="4" t="inlineStr">
-        <is>
-          <t>TZ str. 3 'střední a vrcholovou vaznicí na ocelových sloupcích' + výkres řezu '2x U100' + ChatGPT 'U120 v zalomení'</t>
-        </is>
-      </c>
-      <c r="U137" s="5" t="inlineStr">
-        <is>
-          <t>2× U100 50.02 bm × 10.6 kg/m = 0.53 t + 2× U120 27 bm × 13.4 kg/m = 0.72 t + sloupky cca 6 ks × 100 kg = 0.6 t = celkem 1.85 t ⚠ Statický výpis NUTNÝ — délka, profily, sloupky pouze odhad</t>
+      <c r="R137" t="n">
+        <v>83210</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>calc_traces/statika_assumed.md §4</t>
+        </is>
+      </c>
+      <c r="U137" s="3" t="inlineStr">
+        <is>
+          <t>2× UPN 100 × 50.02 bm × 10.6 kg/m = 1.06 t. Pole sloupků 3.5 m (M_d=11.2 kNm, M_Rd=21.2 kNm, využití 53%, průhyb 1/300 = limit)</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="C138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  &gt;3</t>
-        </is>
-      </c>
-      <c r="E138" t="n">
+      <c r="A138" s="4" t="n"/>
+      <c r="B138" s="4" t="n"/>
+      <c r="C138" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  &gt;3</t>
+        </is>
+      </c>
+      <c r="D138" s="4" t="n"/>
+      <c r="E138" s="4" t="n">
         <v>123</v>
       </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
+      <c r="F138" s="4" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="G138" s="4" t="inlineStr">
         <is>
           <t>PSV</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>767120131</t>
-        </is>
-      </c>
-      <c r="I138" s="3" t="inlineStr">
-        <is>
-          <t>Nadpraží IPE 100 nad přebouranými dveřmi ve střední podélné stěně (2 ks otvorů světlosti 1.0 m)</t>
-        </is>
-      </c>
-      <c r="K138" t="inlineStr">
+      <c r="H138" s="4" t="inlineStr">
+        <is>
+          <t>767120135</t>
+        </is>
+      </c>
+      <c r="I138" s="5" t="inlineStr">
+        <is>
+          <t>Vaznice 2× UPN 120 v zalomení vikýřů — boční vikýře (S235JR, žárově zinkováno)</t>
+        </is>
+      </c>
+      <c r="J138" s="4" t="n"/>
+      <c r="K138" s="4" t="inlineStr">
         <is>
           <t>t</t>
         </is>
       </c>
-      <c r="L138" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="M138" t="n">
+      <c r="L138" s="4" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="M138" s="4" t="n">
         <v>78500</v>
       </c>
-      <c r="N138" t="n">
-        <v>1</v>
-      </c>
-      <c r="O138" t="n">
+      <c r="N138" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O138" s="4" t="n">
         <v>78500</v>
       </c>
-      <c r="R138" t="n">
-        <v>4710</v>
-      </c>
-      <c r="S138" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="T138" t="inlineStr">
-        <is>
-          <t>TZ str. 2 'Jako nadpraží jsou navrženy ocelové profily IPE 100 mm'</t>
-        </is>
-      </c>
-      <c r="U138" s="3" t="inlineStr">
-        <is>
-          <t>2 ks × 1.5 m × 8.1 kg/m × 2 (oboustranné) = 48.6 kg + spojovací = 60 kg</t>
+      <c r="P138" s="4" t="n"/>
+      <c r="Q138" s="4" t="n"/>
+      <c r="R138" s="4" t="n">
+        <v>32185</v>
+      </c>
+      <c r="S138" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="T138" s="4" t="inlineStr">
+        <is>
+          <t>calc_traces/statika_assumed.md §5</t>
+        </is>
+      </c>
+      <c r="U138" s="5" t="inlineStr">
+        <is>
+          <t>2× UPN 120 × 15.24 bm × 13.4 kg/m = 0.41 t. M_d=2.0 kNm &lt;&lt; M_Rd=31.4 kNm (rezerva pro lokální efekty zalomení). ⚠ Délka 15.24 bm (4× 3.81) — pokud výkres D.1.1.2 ukáže jinou délku (až 30 bm), profil má dostatečnou rezervu</t>
         </is>
       </c>
     </row>
@@ -8760,12 +8752,12 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>767995118</t>
+          <t>767120140</t>
         </is>
       </c>
       <c r="I139" s="3" t="inlineStr">
         <is>
-          <t>Antikorozní ochrana ocelových konstrukcí — žárové zinkování / antikorozní nátěr</t>
+          <t>Sloupky pod vaznice 16 ks — trubka 80×60×4 mm, průměrná výška 1.8 m (S235JR, žárově zinkováno)</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -8774,27 +8766,31 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>1.91</v>
+        <v>0.24</v>
       </c>
       <c r="M139" t="n">
-        <v>14500</v>
+        <v>82000</v>
       </c>
       <c r="N139" t="n">
         <v>1</v>
       </c>
       <c r="O139" t="n">
-        <v>14500</v>
+        <v>82000</v>
       </c>
       <c r="R139" t="n">
-        <v>27695</v>
+        <v>19680</v>
       </c>
       <c r="S139" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="T139" t="inlineStr"/>
+        <v>0.82</v>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>calc_traces/statika_assumed.md §6</t>
+        </is>
+      </c>
       <c r="U139" s="3" t="inlineStr">
         <is>
-          <t>celá ocel 1.85 + 0.06 = 1.91 t</t>
+          <t>16 ks × 1.8 m × 8.27 kg/m = 238 kg. F_d=25.6 kN, N_b,Rd=187 kN (využití 14%, χ=0.75 pro L_cr=1.26 m)</t>
         </is>
       </c>
     </row>
@@ -8819,43 +8815,47 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>767995111</t>
+          <t>767120131</t>
         </is>
       </c>
       <c r="I140" s="3" t="inlineStr">
         <is>
-          <t>Kotvení ocelových konstrukcí — chemické / mechanické kotvy</t>
+          <t>Nadpraží IPE 100 nad přebouranými dveřmi ve střední podélné stěně (2 ks otvorů světlosti 1.0 m)</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>t</t>
         </is>
       </c>
       <c r="L140" t="n">
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="M140" t="n">
-        <v>18500</v>
+        <v>78500</v>
       </c>
       <c r="N140" t="n">
         <v>1</v>
       </c>
       <c r="O140" t="n">
-        <v>18500</v>
+        <v>78500</v>
       </c>
       <c r="R140" t="n">
-        <v>18500</v>
+        <v>3925</v>
       </c>
       <c r="S140" t="n">
-        <v>0.7</v>
+        <v>0.92</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
-          <t>TZ str. 3 'Kotvení, spojovací materiál, antikorozní ochrana'</t>
-        </is>
-      </c>
-      <c r="U140" s="3" t="inlineStr"/>
+          <t>TZ str. 2 + calc_traces/statika_assumed.md §9a</t>
+        </is>
+      </c>
+      <c r="U140" s="3" t="inlineStr">
+        <is>
+          <t>2 ks × 1.5 m × 8.1 kg/m × 2 (oboustranné) = 49 kg. Využití 6% (M_d=0.5 kNm, M_Rd=8.8 kNm).</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="C141" t="inlineStr">
@@ -8878,86 +8878,102 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>767996115</t>
+          <t>767995118</t>
         </is>
       </c>
       <c r="I141" s="3" t="inlineStr">
         <is>
-          <t>Tepelně izolační návlek na ocelový profil ve světlíku — minerální vata + povrch hliník</t>
+          <t>Antikorozní ochrana ocelových konstrukcí — žárové zinkování</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="L141" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="M141" t="n">
+        <v>14500</v>
+      </c>
+      <c r="N141" t="n">
+        <v>1</v>
+      </c>
+      <c r="O141" t="n">
+        <v>14500</v>
+      </c>
+      <c r="R141" t="n">
+        <v>25520</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="T141" t="inlineStr"/>
+      <c r="U141" s="3" t="inlineStr">
+        <is>
+          <t>celá ocel 1.06 + 0.41 + 0.24 + 0.05 = 1.76 t</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="C142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  &gt;3</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>127</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>PSV</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>767995111</t>
+        </is>
+      </c>
+      <c r="I142" s="3" t="inlineStr">
+        <is>
+          <t>Kotvení ocelových konstrukcí — chemické / mechanické kotvy</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
           <t>kpl</t>
         </is>
       </c>
-      <c r="L141" t="n">
-        <v>1</v>
-      </c>
-      <c r="M141" t="n">
-        <v>8500</v>
-      </c>
-      <c r="N141" t="n">
-        <v>1</v>
-      </c>
-      <c r="O141" t="n">
-        <v>8500</v>
-      </c>
-      <c r="R141" t="n">
-        <v>8500</v>
-      </c>
-      <c r="S141" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="T141" t="inlineStr">
-        <is>
-          <t>TZ str. 3 'Ocelový profil bude ve světlíku obalen tepelně izolačním návlekem s minerální vatou, povrch – hliník'</t>
-        </is>
-      </c>
-      <c r="U141" s="3" t="inlineStr"/>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="n"/>
-      <c r="B142" s="2" t="n"/>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> &gt;2</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="n"/>
-      <c r="E142" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F142" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G142" s="2" t="n"/>
-      <c r="H142" s="2" t="inlineStr">
-        <is>
-          <t>PSV-771</t>
-        </is>
-      </c>
-      <c r="I142" s="2" t="inlineStr">
-        <is>
-          <t>Podlahy z dlaždic + plovoucí podlaha</t>
-        </is>
-      </c>
-      <c r="J142" s="2" t="n"/>
-      <c r="K142" s="2" t="n"/>
-      <c r="L142" s="2" t="n"/>
-      <c r="M142" s="2" t="n"/>
-      <c r="N142" s="2" t="n"/>
-      <c r="O142" s="2" t="n"/>
-      <c r="P142" s="2" t="n"/>
-      <c r="Q142" s="2" t="n"/>
-      <c r="R142" s="2" t="n">
-        <v>52800</v>
-      </c>
-      <c r="S142" s="2" t="n"/>
-      <c r="T142" s="2" t="n"/>
-      <c r="U142" s="2" t="n"/>
+      <c r="L142" t="n">
+        <v>1</v>
+      </c>
+      <c r="M142" t="n">
+        <v>18500</v>
+      </c>
+      <c r="N142" t="n">
+        <v>1</v>
+      </c>
+      <c r="O142" t="n">
+        <v>18500</v>
+      </c>
+      <c r="R142" t="n">
+        <v>18500</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>TZ str. 3 'Kotvení, spojovací materiál, antikorozní ochrana'</t>
+        </is>
+      </c>
+      <c r="U142" s="3" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="C143" t="inlineStr">
@@ -8966,7 +8982,7 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -8980,47 +8996,43 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>771474112</t>
+          <t>767996115</t>
         </is>
       </c>
       <c r="I143" s="3" t="inlineStr">
         <is>
-          <t>Keramická dlažba lepená do koupelen + WC + zádveří + chodby — formát 30×30 nebo 40×40, mrazuvzdorná, R10</t>
+          <t>Tepelně izolační návlek na ocelový profil ve světlíku — minerální vata + povrch hliník</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="L143" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="M143" t="n">
-        <v>1320</v>
+        <v>8500</v>
       </c>
       <c r="N143" t="n">
         <v>1</v>
       </c>
       <c r="O143" t="n">
-        <v>1320</v>
+        <v>8500</v>
       </c>
       <c r="R143" t="n">
-        <v>52800</v>
+        <v>8500</v>
       </c>
       <c r="S143" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
-          <t>TZ + standard 3+kk</t>
-        </is>
-      </c>
-      <c r="U143" s="3" t="inlineStr">
-        <is>
-          <t>2 byty × cca 20 m2 (koupelna + WC + zádveří + chodba) = 40 m2</t>
-        </is>
-      </c>
+          <t>TZ str. 3 'Ocelový profil bude ve světlíku obalen tepelně izolačním návlekem s minerální vatou, povrch – hliník'</t>
+        </is>
+      </c>
+      <c r="U143" s="3" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n"/>
@@ -9042,12 +9054,12 @@
       <c r="G144" s="2" t="n"/>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>PSV-775</t>
+          <t>PSV-771</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>Podlahy plovoucí</t>
+          <t>Podlahy z dlaždic + plovoucí podlaha</t>
         </is>
       </c>
       <c r="J144" s="2" t="n"/>
@@ -9059,7 +9071,7 @@
       <c r="P144" s="2" t="n"/>
       <c r="Q144" s="2" t="n"/>
       <c r="R144" s="2" t="n">
-        <v>59595</v>
+        <v>52800</v>
       </c>
       <c r="S144" s="2" t="n"/>
       <c r="T144" s="2" t="n"/>
@@ -9072,7 +9084,7 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -9086,12 +9098,12 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>775413232</t>
+          <t>771474112</t>
         </is>
       </c>
       <c r="I145" s="3" t="inlineStr">
         <is>
-          <t>Plovoucí podlaha vícevrstvá lamela / vinyl / korek na podkladovou podložku — obytné místnosti</t>
+          <t>Keramická dlažba lepená do koupelen + WC + zádveří + chodby — formát 30×30 nebo 40×40, mrazuvzdorná, R10</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -9100,31 +9112,31 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>87</v>
+        <v>40</v>
       </c>
       <c r="M145" t="n">
-        <v>685</v>
+        <v>1320</v>
       </c>
       <c r="N145" t="n">
         <v>1</v>
       </c>
       <c r="O145" t="n">
-        <v>685</v>
+        <v>1320</v>
       </c>
       <c r="R145" t="n">
-        <v>59595</v>
+        <v>52800</v>
       </c>
       <c r="S145" t="n">
         <v>0.6</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
-          <t>TZ str. 3 'keramická dlažba nalepená nebo plovoucí podlaha na podložce'</t>
+          <t>TZ + standard 3+kk</t>
         </is>
       </c>
       <c r="U145" s="3" t="inlineStr">
         <is>
-          <t>127 m2 užitná - 40 m2 dlažba = 87 m2</t>
+          <t>2 byty × cca 20 m2 (koupelna + WC + zádveří + chodba) = 40 m2</t>
         </is>
       </c>
     </row>
@@ -9148,12 +9160,12 @@
       <c r="G146" s="2" t="n"/>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>PSV-781</t>
+          <t>PSV-775</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>Obklady keramické</t>
+          <t>Podlahy plovoucí</t>
         </is>
       </c>
       <c r="J146" s="2" t="n"/>
@@ -9165,7 +9177,7 @@
       <c r="P146" s="2" t="n"/>
       <c r="Q146" s="2" t="n"/>
       <c r="R146" s="2" t="n">
-        <v>93575</v>
+        <v>59595</v>
       </c>
       <c r="S146" s="2" t="n"/>
       <c r="T146" s="2" t="n"/>
@@ -9178,7 +9190,7 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -9192,12 +9204,12 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>781474112</t>
+          <t>775413232</t>
         </is>
       </c>
       <c r="I147" s="3" t="inlineStr">
         <is>
-          <t>Keramický obklad stěn koupelen + WC — výška 2.0 m, formát 25×40 / 30×60</t>
+          <t>Plovoucí podlaha vícevrstvá lamela / vinyl / korek na podkladovou podložku — obytné místnosti</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -9206,27 +9218,31 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="M147" t="n">
-        <v>985</v>
+        <v>685</v>
       </c>
       <c r="N147" t="n">
         <v>1</v>
       </c>
       <c r="O147" t="n">
-        <v>985</v>
+        <v>685</v>
       </c>
       <c r="R147" t="n">
-        <v>93575</v>
+        <v>59595</v>
       </c>
       <c r="S147" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="T147" t="inlineStr"/>
+        <v>0.6</v>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>TZ str. 3 'keramická dlažba nalepená nebo plovoucí podlaha na podložce'</t>
+        </is>
+      </c>
       <c r="U147" s="3" t="inlineStr">
         <is>
-          <t>4 koupelny × ~16 m2 obkladu + 2 WC × ~12 m2 + spáry zaokr. = 95 m2</t>
+          <t>127 m2 užitná - 40 m2 dlažba = 87 m2</t>
         </is>
       </c>
     </row>
@@ -9250,12 +9266,12 @@
       <c r="G148" s="2" t="n"/>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>PSV-783</t>
+          <t>PSV-781</t>
         </is>
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>Nátěry + omítky finále</t>
+          <t>Obklady keramické</t>
         </is>
       </c>
       <c r="J148" s="2" t="n"/>
@@ -9267,7 +9283,7 @@
       <c r="P148" s="2" t="n"/>
       <c r="Q148" s="2" t="n"/>
       <c r="R148" s="2" t="n">
-        <v>54625</v>
+        <v>93575</v>
       </c>
       <c r="S148" s="2" t="n"/>
       <c r="T148" s="2" t="n"/>
@@ -9280,7 +9296,7 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -9294,12 +9310,12 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>783325513</t>
+          <t>781474112</t>
         </is>
       </c>
       <c r="I149" s="3" t="inlineStr">
         <is>
-          <t>Vnitřní 2× malířský nátěr bílý na omítky a SDK</t>
+          <t>Keramický obklad stěn koupelen + WC — výška 2.0 m, formát 25×40 / 30×60</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -9308,27 +9324,27 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>575</v>
+        <v>95</v>
       </c>
       <c r="M149" t="n">
-        <v>95</v>
+        <v>985</v>
       </c>
       <c r="N149" t="n">
         <v>1</v>
       </c>
       <c r="O149" t="n">
-        <v>95</v>
+        <v>985</v>
       </c>
       <c r="R149" t="n">
-        <v>54625</v>
+        <v>93575</v>
       </c>
       <c r="S149" t="n">
-        <v>0.75</v>
+        <v>0.55</v>
       </c>
       <c r="T149" t="inlineStr"/>
       <c r="U149" s="3" t="inlineStr">
         <is>
-          <t>omítky 280 + SDK podhled 205.2 + SDK předstěny 90 = 575 m2</t>
+          <t>4 koupelny × ~16 m2 obkladu + 2 WC × ~12 m2 + spáry zaokr. = 95 m2</t>
         </is>
       </c>
     </row>
@@ -9352,12 +9368,12 @@
       <c r="G150" s="2" t="n"/>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>VRN</t>
+          <t>PSV-783</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>Vedlejší rozpočtové náklady</t>
+          <t>Nátěry + omítky finále</t>
         </is>
       </c>
       <c r="J150" s="2" t="n"/>
@@ -9369,7 +9385,7 @@
       <c r="P150" s="2" t="n"/>
       <c r="Q150" s="2" t="n"/>
       <c r="R150" s="2" t="n">
-        <v>271000</v>
+        <v>54625</v>
       </c>
       <c r="S150" s="2" t="n"/>
       <c r="T150" s="2" t="n"/>
@@ -9382,7 +9398,7 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -9391,99 +9407,91 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
+          <t>PSV</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>783325513</t>
+        </is>
+      </c>
+      <c r="I151" s="3" t="inlineStr">
+        <is>
+          <t>Vnitřní 2× malířský nátěr bílý na omítky a SDK</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="L151" t="n">
+        <v>575</v>
+      </c>
+      <c r="M151" t="n">
+        <v>95</v>
+      </c>
+      <c r="N151" t="n">
+        <v>1</v>
+      </c>
+      <c r="O151" t="n">
+        <v>95</v>
+      </c>
+      <c r="R151" t="n">
+        <v>54625</v>
+      </c>
+      <c r="S151" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="T151" t="inlineStr"/>
+      <c r="U151" s="3" t="inlineStr">
+        <is>
+          <t>omítky 280 + SDK podhled 205.2 + SDK předstěny 90 = 575 m2</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="n"/>
+      <c r="B152" s="2" t="n"/>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> &gt;2</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="n"/>
+      <c r="E152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="n"/>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
           <t>VRN</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>030001000</t>
-        </is>
-      </c>
-      <c r="I151" s="3" t="inlineStr">
-        <is>
-          <t>Zařízení staveniště — buňky (kancelář, šatna, sociál), sklady, oplocení, brána, energie + voda, zajištění suti, drobné nářadí</t>
-        </is>
-      </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="L151" t="n">
-        <v>1</v>
-      </c>
-      <c r="M151" t="n">
-        <v>95000</v>
-      </c>
-      <c r="N151" t="n">
-        <v>1</v>
-      </c>
-      <c r="O151" t="n">
-        <v>95000</v>
-      </c>
-      <c r="R151" t="n">
-        <v>95000</v>
-      </c>
-      <c r="S151" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="T151" t="inlineStr"/>
-      <c r="U151" s="3" t="inlineStr"/>
-    </row>
-    <row r="152">
-      <c r="C152" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  &gt;3</t>
-        </is>
-      </c>
-      <c r="E152" t="n">
-        <v>132</v>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>VRN</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>030002000</t>
-        </is>
-      </c>
-      <c r="I152" s="3" t="inlineStr">
-        <is>
-          <t>Koordinátor BOZP — fáze realizace + dokumentace ZS</t>
-        </is>
-      </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="L152" t="n">
-        <v>1</v>
-      </c>
-      <c r="M152" t="n">
-        <v>48000</v>
-      </c>
-      <c r="N152" t="n">
-        <v>1</v>
-      </c>
-      <c r="O152" t="n">
-        <v>48000</v>
-      </c>
-      <c r="R152" t="n">
-        <v>48000</v>
-      </c>
-      <c r="S152" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="T152" t="inlineStr"/>
-      <c r="U152" s="3" t="inlineStr"/>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>Vedlejší rozpočtové náklady</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="n"/>
+      <c r="K152" s="2" t="n"/>
+      <c r="L152" s="2" t="n"/>
+      <c r="M152" s="2" t="n"/>
+      <c r="N152" s="2" t="n"/>
+      <c r="O152" s="2" t="n"/>
+      <c r="P152" s="2" t="n"/>
+      <c r="Q152" s="2" t="n"/>
+      <c r="R152" s="2" t="n">
+        <v>271000</v>
+      </c>
+      <c r="S152" s="2" t="n"/>
+      <c r="T152" s="2" t="n"/>
+      <c r="U152" s="2" t="n"/>
     </row>
     <row r="153">
       <c r="C153" t="inlineStr">
@@ -9506,12 +9514,12 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>030003000</t>
+          <t>030001000</t>
         </is>
       </c>
       <c r="I153" s="3" t="inlineStr">
         <is>
-          <t>Geodetické zaměření před stavbou + skutečné provedení</t>
+          <t>Zařízení staveniště — buňky (kancelář, šatna, sociál), sklady, oplocení, brána, energie + voda, zajištění suti, drobné nářadí</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -9523,19 +9531,19 @@
         <v>1</v>
       </c>
       <c r="M153" t="n">
-        <v>28000</v>
+        <v>95000</v>
       </c>
       <c r="N153" t="n">
         <v>1</v>
       </c>
       <c r="O153" t="n">
-        <v>28000</v>
+        <v>95000</v>
       </c>
       <c r="R153" t="n">
-        <v>28000</v>
+        <v>95000</v>
       </c>
       <c r="S153" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="T153" t="inlineStr"/>
       <c r="U153" s="3" t="inlineStr"/>
@@ -9561,12 +9569,12 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>030004000</t>
+          <t>030002000</t>
         </is>
       </c>
       <c r="I154" s="3" t="inlineStr">
         <is>
-          <t>Průzkum pevnosti zdiva 1.PP + 1.NP — vybrané přitěžované pilíře (TZ §7)</t>
+          <t>Koordinátor BOZP — fáze realizace + dokumentace ZS</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -9578,25 +9586,21 @@
         <v>1</v>
       </c>
       <c r="M154" t="n">
-        <v>35000</v>
+        <v>48000</v>
       </c>
       <c r="N154" t="n">
         <v>1</v>
       </c>
       <c r="O154" t="n">
-        <v>35000</v>
+        <v>48000</v>
       </c>
       <c r="R154" t="n">
-        <v>35000</v>
+        <v>48000</v>
       </c>
       <c r="S154" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="T154" t="inlineStr">
-        <is>
-          <t>TZ str. 7 §7 explicit</t>
-        </is>
-      </c>
+        <v>0.75</v>
+      </c>
+      <c r="T154" t="inlineStr"/>
       <c r="U154" s="3" t="inlineStr"/>
     </row>
     <row r="155">
@@ -9620,12 +9624,12 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>030005000</t>
+          <t>030003000</t>
         </is>
       </c>
       <c r="I155" s="3" t="inlineStr">
         <is>
-          <t>Statický dozor + posouzení skutečného provedení (AD)</t>
+          <t>Geodetické zaměření před stavbou + skutečné provedení</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -9637,19 +9641,19 @@
         <v>1</v>
       </c>
       <c r="M155" t="n">
-        <v>25000</v>
+        <v>28000</v>
       </c>
       <c r="N155" t="n">
         <v>1</v>
       </c>
       <c r="O155" t="n">
-        <v>25000</v>
+        <v>28000</v>
       </c>
       <c r="R155" t="n">
-        <v>25000</v>
+        <v>28000</v>
       </c>
       <c r="S155" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="T155" t="inlineStr"/>
       <c r="U155" s="3" t="inlineStr"/>
@@ -9675,12 +9679,12 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>030006000</t>
+          <t>030004000</t>
         </is>
       </c>
       <c r="I156" s="3" t="inlineStr">
         <is>
-          <t>Pasportizace okolních objektů (sousední BD, navazující fasády) — fotodokumentace + protokol</t>
+          <t>Průzkum pevnosti zdiva 1.PP + 1.NP — vybrané přitěžované pilíře (TZ §7)</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
@@ -9692,21 +9696,25 @@
         <v>1</v>
       </c>
       <c r="M156" t="n">
-        <v>22000</v>
+        <v>35000</v>
       </c>
       <c r="N156" t="n">
         <v>1</v>
       </c>
       <c r="O156" t="n">
-        <v>22000</v>
+        <v>35000</v>
       </c>
       <c r="R156" t="n">
-        <v>22000</v>
+        <v>35000</v>
       </c>
       <c r="S156" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="T156" t="inlineStr"/>
+        <v>0.8</v>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>TZ str. 7 §7 explicit</t>
+        </is>
+      </c>
       <c r="U156" s="3" t="inlineStr"/>
     </row>
     <row r="157">
@@ -9730,12 +9738,12 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>030007000</t>
+          <t>030005000</t>
         </is>
       </c>
       <c r="I157" s="3" t="inlineStr">
         <is>
-          <t>Dokumentace skutečného provedení stavby (DSPS) — všechny profese</t>
+          <t>Statický dozor + posouzení skutečného provedení (AD)</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -9747,51 +9755,161 @@
         <v>1</v>
       </c>
       <c r="M157" t="n">
-        <v>18000</v>
+        <v>25000</v>
       </c>
       <c r="N157" t="n">
         <v>1</v>
       </c>
       <c r="O157" t="n">
-        <v>18000</v>
+        <v>25000</v>
       </c>
       <c r="R157" t="n">
-        <v>18000</v>
+        <v>25000</v>
       </c>
       <c r="S157" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="T157" t="inlineStr"/>
       <c r="U157" s="3" t="inlineStr"/>
     </row>
+    <row r="158">
+      <c r="C158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  &gt;3</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>138</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>VRN</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>030006000</t>
+        </is>
+      </c>
+      <c r="I158" s="3" t="inlineStr">
+        <is>
+          <t>Pasportizace okolních objektů (sousední BD, navazující fasády) — fotodokumentace + protokol</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="L158" t="n">
+        <v>1</v>
+      </c>
+      <c r="M158" t="n">
+        <v>22000</v>
+      </c>
+      <c r="N158" t="n">
+        <v>1</v>
+      </c>
+      <c r="O158" t="n">
+        <v>22000</v>
+      </c>
+      <c r="R158" t="n">
+        <v>22000</v>
+      </c>
+      <c r="S158" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="T158" t="inlineStr"/>
+      <c r="U158" s="3" t="inlineStr"/>
+    </row>
     <row r="159">
-      <c r="I159" s="6" t="inlineStr">
-        <is>
-          <t>CELKEM v2 (bez DPH)</t>
-        </is>
-      </c>
-      <c r="R159" s="7" t="n">
-        <v>3978264</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>DPH 15 % (residential)</t>
-        </is>
-      </c>
-      <c r="R160" t="n">
-        <v>596739.6</v>
-      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  &gt;3</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>139</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>VRN</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>030007000</t>
+        </is>
+      </c>
+      <c r="I159" s="3" t="inlineStr">
+        <is>
+          <t>Dokumentace skutečného provedení stavby (DSPS) — všechny profese</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="L159" t="n">
+        <v>1</v>
+      </c>
+      <c r="M159" t="n">
+        <v>18000</v>
+      </c>
+      <c r="N159" t="n">
+        <v>1</v>
+      </c>
+      <c r="O159" t="n">
+        <v>18000</v>
+      </c>
+      <c r="R159" t="n">
+        <v>18000</v>
+      </c>
+      <c r="S159" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="T159" t="inlineStr"/>
+      <c r="U159" s="3" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="I161" s="6" t="inlineStr">
         <is>
+          <t>CELKEM v2 (bez DPH)</t>
+        </is>
+      </c>
+      <c r="R161" s="7" t="n">
+        <v>3974133</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>DPH 15 % (residential)</t>
+        </is>
+      </c>
+      <c r="R162" t="n">
+        <v>596119.95</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="I163" s="6" t="inlineStr">
+        <is>
           <t>CELKEM s DPH 15 %</t>
         </is>
       </c>
-      <c r="R161" s="7" t="n">
-        <v>4575003.6</v>
+      <c r="R163" s="7" t="n">
+        <v>4570252.95</v>
       </c>
     </row>
   </sheetData>
@@ -9941,10 +10059,10 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>145926</v>
+        <v>154905</v>
       </c>
       <c r="E6" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="7">
@@ -10049,7 +10167,7 @@
         <v>459175</v>
       </c>
       <c r="E11" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="12">
@@ -10127,13 +10245,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>204630</v>
+        <v>191520</v>
       </c>
       <c r="E15" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="16">
@@ -10248,10 +10366,10 @@
         </is>
       </c>
       <c r="C21" s="9" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>3978264</v>
+        <v>3974133</v>
       </c>
       <c r="E21" s="9" t="n">
         <v>100</v>
@@ -10734,7 +10852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -10750,7 +10868,7 @@
     <row r="2">
       <c r="A2" s="12" t="inlineStr">
         <is>
-          <t>STATIKA — krokve, U100, U120, sloupky, zesílení stropu (P0)</t>
+          <t>✅ PRE-STATIKA — krokve 100×180 + pozednice 140×160 + 2× UPN 100 vaznice + 2× UPN 120 zalomení + sloupky trubka 80×60×4 + příložka 100/260 + věnec 250×200 4Φ12 + třmínky Φ8/200 — vše dimenzováno dle Eurokódů (statika_assumed.md). VYŘEŠENO pro fázi nabídky. Pro DPS NUTNO statický posudek ČKAIT IS00.</t>
         </is>
       </c>
     </row>
@@ -10771,19 +10889,33 @@
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
         <is>
-          <t>PBŘ — typy SDK desek, požární odolnost, ucpávky prostupů (P1)</t>
+          <t>PRŮZKUM PEVNOSTI ZDIVA 1.PP + 1.NP — TZ §7 explicit (P0 pro DPS)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>D.1.4 TZB — kanalizace, vodovod, plyn, elektro, vytápění (P1)</t>
+          <t>PRŮZKUM SKUTEČNÉHO STAVU TRÁMŮ — vzorek 4 trámů, vrtná zkouška vlhkost + dřevokazný hmyz (P0 pro DPS)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>PBŘ — typy SDK desek (GKB/GKBi/GKF), požární odolnost EI 30/45/60, ucpávky prostupů (P1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>D.1.4 TZB — kanalizace, vodovod, plyn (2× kotle BAXI Nuvola DUO-TEC), elektro (2× rozvaděč + 2× elektroměr), VZT (4× ventilátor 90 m³/h) (P1, +800k-1.2M Kč)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>Geometrie vikýřů — výška čelní stěny, profil bočních stěn (P1)</t>
         </is>
